--- a/docs/asset-management/PromptCraft_Production_Overview_Simplified.xlsx
+++ b/docs/asset-management/PromptCraft_Production_Overview_Simplified.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Ra1b677cca5734580"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Work" sheetId="2" r:id="R33a6df7595bd42d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File Guide" sheetId="3" r:id="R0a3b9312d2454b2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R86ddacef443d4063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Work" sheetId="2" r:id="R6c69022777564321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File Guide" sheetId="3" r:id="R2ee8bed353df4bec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -82,18 +82,10 @@
   <x:borders count="6">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -205,7 +197,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProductionAreasTable" displayName="ProductionAreasTable" ref="A4:G14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProductionAreasTable" displayName="ProductionAreasTable" ref="A4:G16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Area"/>
     <x:tableColumn id="2" name="Scope"/>
@@ -452,15 +444,15 @@
       <x:c r="A4" s="16" t="str">
         <x:v>Visuals In Use</x:v>
       </x:c>
-      <x:c r="B4" t="str"/>
+      <x:c r="B4"/>
       <x:c r="C4" s="16" t="str">
         <x:v>Visuals To Do</x:v>
       </x:c>
-      <x:c r="D4" t="str"/>
+      <x:c r="D4"/>
       <x:c r="E4" s="16" t="str">
         <x:v>Voice Lines To Record</x:v>
       </x:c>
-      <x:c r="F4" t="str"/>
+      <x:c r="F4"/>
       <x:c r="G4" s="16" t="str">
         <x:v>Runtime Audio In Use</x:v>
       </x:c>
@@ -468,23 +460,26 @@
     </x:row>
     <x:row r="5" ht="36" customHeight="1">
       <x:c r="A5" s="21" t="n">
-        <x:v>28</x:v>
-      </x:c>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B5"/>
       <x:c r="C5" s="21" t="n">
-        <x:v>32</x:v>
-      </x:c>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D5"/>
       <x:c r="E5" s="21" t="n">
-        <x:v>58</x:v>
-      </x:c>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F5"/>
       <x:c r="G5" s="21" t="n">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="26" t="str">
         <x:v>What this workbook is for</x:v>
       </x:c>
-      <x:c r="B8" s="26" t="str"/>
+      <x:c r="B8" s="26"/>
       <x:c r="C8" s="26" t="str"/>
       <x:c r="D8" s="26" t="str"/>
       <x:c r="E8" s="26" t="str"/>
@@ -525,7 +520,7 @@
         <x:v>Voice / recording detail</x:v>
       </x:c>
       <x:c r="B11" s="29" t="str">
-        <x:v>Open PromptCraft_Voiceover_Tracker_Simplified.xlsx</x:v>
+        <x:v>Open PromptCraft_Voice_Recording_Tracker.xlsx</x:v>
       </x:c>
       <x:c r="C11" s="29" t="str"/>
       <x:c r="D11" s="29" t="str"/>
@@ -539,7 +534,7 @@
         <x:v>Current technical baseline</x:v>
       </x:c>
       <x:c r="B12" s="29" t="str">
-        <x:v>PROMPTCRAFT_V429 · schema V121 · receiver V82</x:v>
+        <x:v>PROMPTCRAFT_V429 · schema V121 · patch 527 · receiver V83 live / V84 candidate · proxy V373 · asset manifest v149</x:v>
       </x:c>
       <x:c r="C12" s="29" t="str"/>
       <x:c r="D12" s="29" t="str"/>
@@ -651,16 +646,16 @@
         <x:v>Visual</x:v>
       </x:c>
       <x:c r="C6" s="44" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D6" s="44" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="44" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="F6" s="44" t="str">
-        <x:v>Review pending assets</x:v>
+        <x:v>Review three planned or locked scene assets</x:v>
       </x:c>
       <x:c r="G6" s="44" t="str">
         <x:v>Visual Asset Tracker</x:v>
@@ -668,22 +663,22 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="44" t="str">
-        <x:v>Character</x:v>
+        <x:v>Canvas evidence</x:v>
       </x:c>
       <x:c r="B7" s="44" t="str">
         <x:v>Visual</x:v>
       </x:c>
       <x:c r="C7" s="44" t="n">
-        <x:v>6</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D7" s="44" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E7" s="44" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="F7" s="44" t="str">
-        <x:v>Maintain current assets</x:v>
+        <x:v>Maintain current S1 evidence set</x:v>
       </x:c>
       <x:c r="G7" s="44" t="str">
         <x:v>Visual Asset Tracker</x:v>
@@ -691,22 +686,22 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="44" t="str">
-        <x:v>Student portrait</x:v>
+        <x:v>Character</x:v>
       </x:c>
       <x:c r="B8" s="44" t="str">
         <x:v>Visual</x:v>
       </x:c>
       <x:c r="C8" s="44" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="44" t="n">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E8" s="44" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="F8" s="44" t="str">
-        <x:v>Review pending assets</x:v>
+        <x:v>Maintain Professor Pixel portraits</x:v>
       </x:c>
       <x:c r="G8" s="44" t="str">
         <x:v>Visual Asset Tracker</x:v>
@@ -714,22 +709,22 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="44" t="str">
-        <x:v>UI / Babbage</x:v>
+        <x:v>Student portrait</x:v>
       </x:c>
       <x:c r="B9" s="44" t="str">
         <x:v>Visual</x:v>
       </x:c>
       <x:c r="C9" s="44" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="44" t="n">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E9" s="44" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="F9" s="44" t="str">
-        <x:v>Maintain current assets</x:v>
+        <x:v>Create future S5–S7 portraits after scenarios lock</x:v>
       </x:c>
       <x:c r="G9" s="44" t="str">
         <x:v>Visual Asset Tracker</x:v>
@@ -737,13 +732,13 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="44" t="str">
-        <x:v>Brand / Print</x:v>
+        <x:v>UI / Babbage</x:v>
       </x:c>
       <x:c r="B10" s="44" t="str">
         <x:v>Visual</x:v>
       </x:c>
       <x:c r="C10" s="44" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D10" s="44" t="n">
         <x:v>0</x:v>
@@ -760,22 +755,22 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="44" t="str">
-        <x:v>UI / Utility</x:v>
+        <x:v>Brand / Print</x:v>
       </x:c>
       <x:c r="B11" s="44" t="str">
         <x:v>Visual</x:v>
       </x:c>
       <x:c r="C11" s="44" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="44" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="44" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="F11" s="44" t="str">
-        <x:v>Maintain current assets</x:v>
+        <x:v>Standalone logo archived; print uses text affiliation</x:v>
       </x:c>
       <x:c r="G11" s="44" t="str">
         <x:v>Visual Asset Tracker</x:v>
@@ -783,30 +778,30 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="44" t="str">
-        <x:v>Professor Pixel</x:v>
+        <x:v>UI / Utility</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
-        <x:v>Voiceover</x:v>
+        <x:v>Visual</x:v>
       </x:c>
       <x:c r="C12" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" s="44" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="44" t="n">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="E12" s="44" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="F12" s="44" t="str">
-        <x:v>Record current active script</x:v>
+        <x:v>Maintain current asset</x:v>
       </x:c>
       <x:c r="G12" s="44" t="str">
-        <x:v>Voiceover Tracker</x:v>
+        <x:v>Visual Asset Tracker</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="44" t="str">
-        <x:v>Jordan</x:v>
+        <x:v>Professor Pixel</x:v>
       </x:c>
       <x:c r="B13" s="44" t="str">
         <x:v>Voiceover</x:v>
@@ -815,38 +810,84 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="44" t="n">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E13" s="44" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="F13" s="44" t="str">
-        <x:v>Review wording, then record S2 script</x:v>
+        <x:v>Record current active script</x:v>
       </x:c>
       <x:c r="G13" s="44" t="str">
-        <x:v>Voiceover Tracker</x:v>
+        <x:v>Voice Recording Tracker</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="45" t="str">
+        <x:v>Eli</x:v>
+      </x:c>
+      <x:c r="B14" s="45" t="str">
+        <x:v>Voiceover</x:v>
+      </x:c>
+      <x:c r="C14" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="45" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E14" s="45" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F14" s="45" t="str">
+        <x:v>Record current S1 script</x:v>
+      </x:c>
+      <x:c r="G14" s="45" t="str">
+        <x:v>Voice Recording Tracker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Jordan</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Voiceover</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Record current S3 script; retain legacy filenames</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Voice Recording Tracker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
         <x:v>Runtime Audio</x:v>
       </x:c>
-      <x:c r="B14" s="45" t="str">
+      <x:c r="B16" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="C14" s="45" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D14" s="45" t="n">
+      <x:c r="C16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="45" t="str">
+      <x:c r="E16" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F14" s="45" t="str">
-        <x:v>Maintain current runtime files</x:v>
-      </x:c>
-      <x:c r="G14" s="45" t="str">
+      <x:c r="F16" t="str">
+        <x:v>Maintain three loaded runtime files</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
         <x:v>Production Overview</x:v>
       </x:c>
     </x:row>
@@ -855,14 +896,17 @@
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="E5:E14">
+      <x:formula1>"High,Medium,Low"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E5:E16">
       <x:formula1>"High,Medium,Low"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5350eea8714548bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b7d9eabab044611"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -926,7 +970,7 @@
         <x:v>PromptCraft_Visual_Asset_Tracker_Simplified.xlsx</x:v>
       </x:c>
       <x:c r="B6" s="44" t="str">
-        <x:v>Images, backgrounds, characters, scene art, Babbage/brand visuals</x:v>
+        <x:v>Images, backgrounds, characters, scene art, Canvas evidence, and Babbage/brand visuals</x:v>
       </x:c>
       <x:c r="C6" s="44" t="str">
         <x:v>Dialogue recording</x:v>
@@ -937,16 +981,16 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="45" t="str">
-        <x:v>PromptCraft_Voiceover_Tracker_Simplified.xlsx</x:v>
+        <x:v>PromptCraft_Voice_Recording_Tracker.xlsx</x:v>
       </x:c>
       <x:c r="B7" s="45" t="str">
-        <x:v>Current recording queue and dynamic/optional line decisions</x:v>
+        <x:v>Current recording queue and dynamic or optional line decisions</x:v>
       </x:c>
       <x:c r="C7" s="45" t="str">
         <x:v>Legacy dialogue history</x:v>
       </x:c>
       <x:c r="D7" s="45" t="str">
-        <x:v>Summary; Recording Queue; Needs Decision</x:v>
+        <x:v>Start Here; Recording Queue; Needs Decision; Retired</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
